--- a/data/trans_dic/PCS12_SP_R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R3-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12)</t>
+          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,58; 21,85</t>
+          <t>12,88; 21,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,39; 26,23</t>
+          <t>16,99; 26,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,92; 25,74</t>
+          <t>16,39; 25,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,48; 27,41</t>
+          <t>17,51; 26,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,19; 29,92</t>
+          <t>19,04; 29,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,24; 40,59</t>
+          <t>29,11; 41,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,19; 40,6</t>
+          <t>29,91; 41,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,42; 39,01</t>
+          <t>29,53; 39,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,02; 24,14</t>
+          <t>17,12; 24,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,34; 31,93</t>
+          <t>24,32; 32,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,18; 31,48</t>
+          <t>24,05; 32,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,51; 31,37</t>
+          <t>24,5; 31,26</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,75; 19,46</t>
+          <t>12,77; 19,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,09; 19,34</t>
+          <t>12,12; 19,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,76; 16,58</t>
+          <t>10,71; 16,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,99; 26,7</t>
+          <t>17,85; 26,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,69; 34,82</t>
+          <t>27,17; 34,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,68; 32,7</t>
+          <t>24,37; 32,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,51; 26,65</t>
+          <t>18,84; 26,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,81; 33,72</t>
+          <t>27,11; 33,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,47; 26,23</t>
+          <t>20,75; 26,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,93; 24,68</t>
+          <t>19,55; 24,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,55; 20,35</t>
+          <t>15,46; 20,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,37; 28,91</t>
+          <t>23,43; 28,79</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,84; 17,28</t>
+          <t>9,87; 17,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,34; 20,91</t>
+          <t>12,28; 21,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,69; 17,74</t>
+          <t>10,63; 17,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,75; 30,72</t>
+          <t>21,39; 30,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,11; 33,04</t>
+          <t>24,06; 33,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,07; 31,01</t>
+          <t>21,02; 31,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,94; 24,14</t>
+          <t>15,44; 24,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,11; 34,89</t>
+          <t>26,87; 35,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,88; 24,38</t>
+          <t>17,74; 23,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,82; 24,13</t>
+          <t>17,95; 24,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,18; 20,06</t>
+          <t>13,74; 19,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,41; 31,58</t>
+          <t>25,5; 31,67</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,53; 17,94</t>
+          <t>10,72; 17,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,5; 26,72</t>
+          <t>17,63; 26,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,89; 27,4</t>
+          <t>18,76; 28,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,71; 30,94</t>
+          <t>20,23; 31,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,32; 32,08</t>
+          <t>23,28; 32,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,4; 42,06</t>
+          <t>32,08; 42,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,59; 41,85</t>
+          <t>31,84; 41,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,18; 34,68</t>
+          <t>16,05; 34,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,1; 24,19</t>
+          <t>17,78; 23,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,16; 32,91</t>
+          <t>26,33; 32,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,33; 33,97</t>
+          <t>26,52; 33,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,27; 31,07</t>
+          <t>18,79; 31,26</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,12; 18,25</t>
+          <t>9,38; 19,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,11; 29,27</t>
+          <t>17,06; 29,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,2; 19,59</t>
+          <t>10,23; 19,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,7; 20,37</t>
+          <t>11,76; 20,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,82; 27,93</t>
+          <t>16,5; 28,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,39; 45,22</t>
+          <t>31,6; 45,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,43; 28,99</t>
+          <t>18,01; 29,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,18; 28,7</t>
+          <t>21,03; 29,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,17; 21,38</t>
+          <t>14,28; 21,57</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,18; 35,17</t>
+          <t>26,46; 34,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,27; 22,53</t>
+          <t>15,34; 22,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,76; 23,18</t>
+          <t>17,7; 23,41</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,04; 22,05</t>
+          <t>12,78; 21,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,51; 27,27</t>
+          <t>17,6; 27,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,74; 29,2</t>
+          <t>18,78; 29,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,5; 34,06</t>
+          <t>24,61; 33,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,64; 37,07</t>
+          <t>25,86; 36,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,11; 35,04</t>
+          <t>24,87; 35,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,46; 36,19</t>
+          <t>25,55; 36,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33,54; 42,97</t>
+          <t>33,73; 42,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,75; 28,17</t>
+          <t>20,88; 27,8</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22,08; 29,87</t>
+          <t>22,74; 29,8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23,45; 31,49</t>
+          <t>23,53; 31,42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30,53; 37,29</t>
+          <t>30,41; 36,86</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,05; 18,81</t>
+          <t>13,1; 18,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,45; 18,05</t>
+          <t>12,27; 17,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,21; 21,63</t>
+          <t>15,56; 21,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,09; 23,86</t>
+          <t>17,51; 24,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,17; 28,99</t>
+          <t>22,19; 29,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,37; 30,24</t>
+          <t>23,45; 30,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,64; 29,74</t>
+          <t>22,88; 30,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,71; 31,49</t>
+          <t>11,4; 31,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,36; 23,1</t>
+          <t>18,43; 22,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,59; 23,32</t>
+          <t>18,7; 23,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20,2; 25,13</t>
+          <t>20,2; 24,79</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,61; 26,35</t>
+          <t>13,31; 26,16</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,19; 20,58</t>
+          <t>15,17; 20,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,54; 20,13</t>
+          <t>14,3; 19,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,31; 14,94</t>
+          <t>10,25; 14,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,08; 72,97</t>
+          <t>15,88; 71,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,5; 29,97</t>
+          <t>23,65; 30,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,61; 27,73</t>
+          <t>21,4; 27,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,3; 25,75</t>
+          <t>19,56; 25,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>24,35; 30,34</t>
+          <t>24,43; 29,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,34; 24,57</t>
+          <t>20,01; 24,49</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18,81; 23,19</t>
+          <t>18,8; 23,14</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15,62; 19,66</t>
+          <t>15,53; 19,33</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,43; 58,96</t>
+          <t>21,49; 61,12</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14,65; 17,11</t>
+          <t>14,48; 17,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,72; 19,22</t>
+          <t>16,61; 19,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,43; 17,96</t>
+          <t>15,5; 18,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21,12; 46,85</t>
+          <t>21,09; 42,99</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25,62; 28,75</t>
+          <t>25,71; 28,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,55; 30,6</t>
+          <t>27,49; 30,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,67; 27,76</t>
+          <t>24,69; 27,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23,57; 30,69</t>
+          <t>22,89; 30,63</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,52; 22,62</t>
+          <t>20,48; 22,61</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22,61; 24,69</t>
+          <t>22,64; 24,7</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20,46; 22,54</t>
+          <t>20,49; 22,52</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24,18; 35,49</t>
+          <t>24,29; 36,84</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12)</t>
+          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34342; 59647</t>
+          <t>35163; 58882</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48320; 77308</t>
+          <t>50062; 78690</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46778; 75614</t>
+          <t>48145; 76289</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54446; 85359</t>
+          <t>54526; 83329</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>50059; 78030</t>
+          <t>49666; 78104</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83983; 116602</t>
+          <t>83616; 118093</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84283; 117208</t>
+          <t>86347; 118618</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>85223; 112988</t>
+          <t>85527; 113714</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>90862; 128853</t>
+          <t>91392; 130543</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>141650; 185836</t>
+          <t>141525; 187470</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140840; 183377</t>
+          <t>140098; 187137</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>147319; 188561</t>
+          <t>147234; 187880</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62887; 95930</t>
+          <t>62943; 96900</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61136; 97768</t>
+          <t>61251; 96723</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54075; 83352</t>
+          <t>53819; 84712</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>93114; 138177</t>
+          <t>92383; 138489</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>134488; 175452</t>
+          <t>136905; 175656</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>129281; 171251</t>
+          <t>127638; 170384</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96815; 139395</t>
+          <t>98533; 137511</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>137686; 173177</t>
+          <t>139231; 174389</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>204118; 261495</t>
+          <t>206895; 261974</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>194883; 253984</t>
+          <t>201207; 255024</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>159468; 208716</t>
+          <t>158605; 208846</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>240942; 298054</t>
+          <t>241628; 296833</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31370; 55108</t>
+          <t>31459; 55600</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39991; 67758</t>
+          <t>39787; 68075</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34067; 56516</t>
+          <t>33855; 55768</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68299; 96498</t>
+          <t>67191; 95148</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>77529; 110806</t>
+          <t>80705; 112372</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71859; 105736</t>
+          <t>71677; 106539</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50239; 81181</t>
+          <t>51923; 82187</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>93286; 120067</t>
+          <t>92477; 121366</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>116953; 159510</t>
+          <t>116091; 156157</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>118515; 160484</t>
+          <t>119402; 162492</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>92861; 131380</t>
+          <t>89950; 128077</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>167243; 207857</t>
+          <t>167853; 208430</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37764; 64333</t>
+          <t>38440; 64076</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65458; 99924</t>
+          <t>65934; 97508</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69897; 101372</t>
+          <t>69408; 104042</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60341; 94735</t>
+          <t>61939; 95107</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>86613; 119149</t>
+          <t>86492; 121110</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>126030; 163582</t>
+          <t>124793; 164105</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>122357; 162086</t>
+          <t>123292; 162572</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>80811; 163153</t>
+          <t>75516; 163128</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>132127; 176582</t>
+          <t>129851; 173662</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>199591; 251100</t>
+          <t>200876; 250493</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>199421; 257271</t>
+          <t>200798; 252827</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>149699; 241337</t>
+          <t>145955; 242765</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18552; 37101</t>
+          <t>19062; 38797</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>36383; 62233</t>
+          <t>36266; 62082</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21546; 41369</t>
+          <t>21616; 41663</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20853; 36300</t>
+          <t>20962; 35660</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32843; 58005</t>
+          <t>34272; 58195</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>68934; 99295</t>
+          <t>69392; 99772</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38111; 63370</t>
+          <t>39364; 63854</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>43765; 59313</t>
+          <t>43451; 60145</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>58223; 87881</t>
+          <t>58686; 88659</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>113167; 152002</t>
+          <t>114359; 150942</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65641; 96842</t>
+          <t>65912; 98712</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>68360; 89223</t>
+          <t>68128; 90115</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>35315; 59711</t>
+          <t>34600; 59415</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>47963; 74718</t>
+          <t>48213; 74236</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49314; 76833</t>
+          <t>49407; 77710</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65952; 91687</t>
+          <t>66252; 90759</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>71322; 103106</t>
+          <t>71940; 102338</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67510; 98119</t>
+          <t>69648; 100298</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>66810; 98846</t>
+          <t>69775; 100063</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>86220; 110444</t>
+          <t>86693; 110266</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>113911; 154623</t>
+          <t>114613; 152608</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>122300; 165472</t>
+          <t>125993; 165111</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>125749; 168882</t>
+          <t>126183; 168463</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>160678; 196203</t>
+          <t>160045; 193964</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>80259; 115667</t>
+          <t>80560; 114856</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>82540; 119620</t>
+          <t>81350; 118685</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>99842; 141996</t>
+          <t>102133; 141023</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>105950; 147931</t>
+          <t>108535; 150371</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>141523; 185017</t>
+          <t>141605; 186975</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>162133; 209801</t>
+          <t>162692; 210312</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>156495; 205575</t>
+          <t>158183; 208092</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>82247; 266646</t>
+          <t>96541; 267604</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>230034; 289492</t>
+          <t>230993; 288009</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>252147; 316315</t>
+          <t>253679; 316903</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>272301; 338737</t>
+          <t>272330; 334097</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>199634; 386549</t>
+          <t>195237; 383706</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>112969; 153102</t>
+          <t>112866; 151861</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>113317; 156844</t>
+          <t>111445; 155154</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>80252; 116334</t>
+          <t>79771; 116282</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>149136; 676558</t>
+          <t>147226; 667445</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>184115; 234853</t>
+          <t>185300; 237694</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>178017; 228460</t>
+          <t>176324; 226799</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>159465; 212720</t>
+          <t>161588; 210249</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>174173; 217034</t>
+          <t>174763; 212498</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>310647; 375192</t>
+          <t>305647; 374031</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>301573; 371803</t>
+          <t>301293; 370896</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>250587; 315518</t>
+          <t>249191; 310155</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>351986; 968327</t>
+          <t>353009; 1003850</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>479996; 560644</t>
+          <t>474454; 560810</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>573040; 658524</t>
+          <t>569321; 661015</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>523746; 609668</t>
+          <t>525968; 616499</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>727315; 1613373</t>
+          <t>726198; 1480569</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>865860; 971428</t>
+          <t>868738; 973390</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>980169; 1088966</t>
+          <t>978146; 1093802</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>874369; 984036</t>
+          <t>875309; 985535</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>858752; 1118072</t>
+          <t>833870; 1116157</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1365870; 1505658</t>
+          <t>1362956; 1504916</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1579453; 1724670</t>
+          <t>1581308; 1725508</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1419595; 1563796</t>
+          <t>1422095; 1562434</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1713593; 2514992</t>
+          <t>1721211; 2611019</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/PCS12_SP_R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R3-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,88; 21,57</t>
+          <t>12,7; 21,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,99; 26,7</t>
+          <t>16,78; 26,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,39; 25,97</t>
+          <t>16,14; 26,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,51; 26,76</t>
+          <t>17,41; 25,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,04; 29,94</t>
+          <t>18,68; 29,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,11; 41,11</t>
+          <t>29,16; 40,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,91; 41,09</t>
+          <t>29,6; 40,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,53; 39,26</t>
+          <t>28,88; 37,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,12; 24,45</t>
+          <t>16,91; 23,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,32; 32,21</t>
+          <t>23,96; 31,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,05; 32,13</t>
+          <t>23,89; 31,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,5; 31,26</t>
+          <t>24,52; 30,49</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,31%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,77; 19,65</t>
+          <t>12,59; 19,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,12; 19,13</t>
+          <t>12,13; 19,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,71; 16,86</t>
+          <t>10,62; 16,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,85; 26,76</t>
+          <t>18,72; 26,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,17; 34,86</t>
+          <t>26,97; 34,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,37; 32,53</t>
+          <t>24,58; 32,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,84; 26,29</t>
+          <t>18,31; 25,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,11; 33,96</t>
+          <t>26,88; 33,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,75; 26,28</t>
+          <t>20,83; 26,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,55; 24,78</t>
+          <t>19,39; 24,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,46; 20,36</t>
+          <t>15,55; 20,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,43; 28,79</t>
+          <t>23,54; 28,84</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,87; 17,44</t>
+          <t>9,56; 17,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,28; 21,01</t>
+          <t>12,06; 20,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,63; 17,51</t>
+          <t>10,41; 17,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,39; 30,29</t>
+          <t>21,62; 30,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,06; 33,5</t>
+          <t>23,78; 33,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,02; 31,24</t>
+          <t>20,77; 30,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,44; 24,44</t>
+          <t>15,47; 24,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,87; 35,27</t>
+          <t>26,93; 34,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,74; 23,87</t>
+          <t>18,1; 24,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,95; 24,43</t>
+          <t>17,8; 24,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,74; 19,56</t>
+          <t>13,81; 19,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,5; 31,67</t>
+          <t>25,32; 31,2</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,72; 17,86</t>
+          <t>10,64; 18,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,63; 26,07</t>
+          <t>17,49; 26,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,76; 28,12</t>
+          <t>18,91; 27,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,23; 31,06</t>
+          <t>19,14; 30,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,28; 32,6</t>
+          <t>23,68; 32,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,08; 42,19</t>
+          <t>32,32; 42,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,84; 41,98</t>
+          <t>31,55; 41,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,05; 34,67</t>
+          <t>30,17; 38,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,78; 23,79</t>
+          <t>18,3; 23,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,33; 32,83</t>
+          <t>26,21; 32,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,52; 33,39</t>
+          <t>26,48; 33,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,79; 31,26</t>
+          <t>26,2; 33,07</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,38; 19,08</t>
+          <t>9,5; 18,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,06; 29,2</t>
+          <t>16,94; 28,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,23; 19,72</t>
+          <t>10,03; 19,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,76; 20,01</t>
+          <t>10,99; 19,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,5; 28,02</t>
+          <t>16,1; 27,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,6; 45,44</t>
+          <t>32,03; 44,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,01; 29,21</t>
+          <t>17,64; 28,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,03; 29,11</t>
+          <t>20,37; 27,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,28; 21,57</t>
+          <t>14,04; 21,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,46; 34,92</t>
+          <t>26,42; 35,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,34; 22,97</t>
+          <t>15,33; 22,81</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,7; 23,41</t>
+          <t>16,93; 22,2</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,78; 21,94</t>
+          <t>13,01; 21,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,6; 27,1</t>
+          <t>17,78; 27,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,78; 29,53</t>
+          <t>19,02; 29,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,61; 33,72</t>
+          <t>23,88; 33,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,86; 36,79</t>
+          <t>26,36; 37,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,87; 35,82</t>
+          <t>24,23; 35,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,55; 36,64</t>
+          <t>24,7; 36,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33,73; 42,9</t>
+          <t>33,23; 42,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,88; 27,8</t>
+          <t>20,68; 28,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22,74; 29,8</t>
+          <t>22,11; 29,57</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23,53; 31,42</t>
+          <t>23,59; 31,39</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30,41; 36,86</t>
+          <t>29,94; 36,53</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,1; 18,68</t>
+          <t>12,66; 18,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,27; 17,91</t>
+          <t>12,13; 18,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,56; 21,48</t>
+          <t>15,41; 21,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,51; 24,26</t>
+          <t>17,35; 23,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,19; 29,3</t>
+          <t>22,2; 29,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,45; 30,31</t>
+          <t>23,38; 30,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,88; 30,1</t>
+          <t>22,57; 29,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,4; 31,6</t>
+          <t>28,06; 33,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,43; 22,98</t>
+          <t>18,36; 22,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,7; 23,36</t>
+          <t>18,71; 23,47</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20,2; 24,79</t>
+          <t>20,05; 24,76</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,31; 26,16</t>
+          <t>24,14; 28,42</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,17; 20,42</t>
+          <t>15,1; 20,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,3; 19,91</t>
+          <t>14,19; 20,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,25; 14,94</t>
+          <t>10,14; 14,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,88; 71,99</t>
+          <t>13,94; 19,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,65; 30,34</t>
+          <t>23,59; 30,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,4; 27,53</t>
+          <t>21,43; 27,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,56; 25,45</t>
+          <t>19,37; 25,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>24,43; 29,71</t>
+          <t>23,37; 28,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,01; 24,49</t>
+          <t>20,25; 24,46</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18,8; 23,14</t>
+          <t>18,69; 22,86</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15,53; 19,33</t>
+          <t>15,58; 19,47</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,49; 61,12</t>
+          <t>19,8; 23,33</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14,48; 17,12</t>
+          <t>14,68; 17,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,61; 19,29</t>
+          <t>16,44; 19,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,5; 18,16</t>
+          <t>15,46; 18,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21,09; 42,99</t>
+          <t>19,83; 22,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25,71; 28,81</t>
+          <t>25,72; 28,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,49; 30,74</t>
+          <t>27,51; 30,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,69; 27,8</t>
+          <t>24,49; 27,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22,89; 30,63</t>
+          <t>29,1; 31,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,48; 22,61</t>
+          <t>20,61; 22,62</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22,64; 24,7</t>
+          <t>22,65; 24,66</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20,49; 22,52</t>
+          <t>20,43; 22,54</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24,29; 36,84</t>
+          <t>24,92; 26,82</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68014</t>
+          <t>68402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>98234</t>
+          <t>105270</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>166248</t>
+          <t>173673</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35163; 58882</t>
+          <t>34683; 59086</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50062; 78690</t>
+          <t>49460; 77867</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48145; 76289</t>
+          <t>47402; 77252</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54526; 83329</t>
+          <t>55518; 82736</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>49666; 78104</t>
+          <t>48716; 77584</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83616; 118093</t>
+          <t>83759; 117620</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86347; 118618</t>
+          <t>85465; 118146</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>85527; 113714</t>
+          <t>91294; 119429</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>91392; 130543</t>
+          <t>90285; 127985</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>141525; 187470</t>
+          <t>139472; 184853</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140098; 187137</t>
+          <t>139127; 182918</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>147234; 187880</t>
+          <t>155686; 193554</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114027</t>
+          <t>120046</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>155840</t>
+          <t>162691</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>269867</t>
+          <t>282737</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62943; 96900</t>
+          <t>62060; 95924</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61251; 96723</t>
+          <t>61317; 98152</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53819; 84712</t>
+          <t>53362; 82427</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>92383; 138489</t>
+          <t>99130; 141512</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>136905; 175656</t>
+          <t>135898; 175042</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>127638; 170384</t>
+          <t>128731; 172068</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>98533; 137511</t>
+          <t>95801; 135948</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>139231; 174389</t>
+          <t>146491; 182465</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>206895; 261974</t>
+          <t>207632; 261118</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>201207; 255024</t>
+          <t>199562; 254746</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>158605; 208846</t>
+          <t>159461; 210501</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>241628; 296833</t>
+          <t>252934; 309929</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80739</t>
+          <t>81607</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>106912</t>
+          <t>107692</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>187651</t>
+          <t>189299</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31459; 55600</t>
+          <t>30484; 54614</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39787; 68075</t>
+          <t>39085; 66333</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33855; 55768</t>
+          <t>33151; 56953</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67191; 95148</t>
+          <t>67916; 97245</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>80705; 112372</t>
+          <t>79772; 111722</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71677; 106539</t>
+          <t>70819; 103508</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51923; 82187</t>
+          <t>52036; 82869</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>92477; 121366</t>
+          <t>94645; 121792</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>116091; 156157</t>
+          <t>118417; 160022</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>119402; 162492</t>
+          <t>118362; 162973</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89950; 128077</t>
+          <t>90423; 129868</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>167853; 208430</t>
+          <t>168523; 207619</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78009</t>
+          <t>89182</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>127986</t>
+          <t>142645</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>205995</t>
+          <t>231826</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38440; 64076</t>
+          <t>38151; 64992</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65934; 97508</t>
+          <t>65412; 98725</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69408; 104042</t>
+          <t>69946; 103462</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61939; 95107</t>
+          <t>70071; 110850</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>86492; 121110</t>
+          <t>87960; 121443</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>124793; 164105</t>
+          <t>125706; 164268</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>123292; 162572</t>
+          <t>122188; 162534</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>75516; 163128</t>
+          <t>125633; 161779</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>129851; 173662</t>
+          <t>133586; 174862</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>200876; 250493</t>
+          <t>199991; 250434</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>200798; 252827</t>
+          <t>200503; 253503</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>145955; 242765</t>
+          <t>205059; 258763</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27461</t>
+          <t>29929</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51046</t>
+          <t>53660</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78508</t>
+          <t>83589</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19062; 38797</t>
+          <t>19315; 38086</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>36266; 62082</t>
+          <t>36027; 61407</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21616; 41663</t>
+          <t>21189; 40988</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20962; 35660</t>
+          <t>22546; 39381</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>34272; 58195</t>
+          <t>33434; 57387</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69392; 99772</t>
+          <t>70328; 98623</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39364; 63854</t>
+          <t>38563; 63343</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>43451; 60145</t>
+          <t>45867; 62590</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>58686; 88659</t>
+          <t>57694; 89965</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>114359; 150942</t>
+          <t>114183; 153753</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65912; 98712</t>
+          <t>65873; 98022</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>68128; 90115</t>
+          <t>72841; 95538</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77848</t>
+          <t>75968</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>97947</t>
+          <t>100275</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>175794</t>
+          <t>176243</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>34600; 59415</t>
+          <t>35223; 58707</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48213; 74236</t>
+          <t>48724; 75968</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49407; 77710</t>
+          <t>50047; 76834</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>66252; 90759</t>
+          <t>64518; 89287</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>71940; 102338</t>
+          <t>73332; 103240</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>69648; 100298</t>
+          <t>67854; 99424</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>69775; 100063</t>
+          <t>67466; 99557</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>86693; 110266</t>
+          <t>87634; 112420</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>114613; 152608</t>
+          <t>113499; 153867</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>125993; 165111</t>
+          <t>122475; 163825</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>126183; 168463</t>
+          <t>126484; 168344</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>160045; 193964</t>
+          <t>159892; 195045</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>126749</t>
+          <t>148731</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>195232</t>
+          <t>238187</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>321981</t>
+          <t>386919</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>80560; 114856</t>
+          <t>77858; 115213</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>81350; 118685</t>
+          <t>80398; 119441</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>102133; 141023</t>
+          <t>101177; 140465</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>108535; 150371</t>
+          <t>123987; 171012</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>141605; 186975</t>
+          <t>141665; 185658</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>162692; 210312</t>
+          <t>162209; 209163</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>158183; 208092</t>
+          <t>156023; 206123</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>96541; 267604</t>
+          <t>215918; 259458</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>230993; 288009</t>
+          <t>230096; 287938</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>253679; 316903</t>
+          <t>253783; 318372</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>272330; 334097</t>
+          <t>270291; 333774</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>195237; 383706</t>
+          <t>358263; 421677</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>359818</t>
+          <t>129911</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>192119</t>
+          <t>216642</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>551937</t>
+          <t>346552</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>112866; 151861</t>
+          <t>112278; 154480</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>111445; 155154</t>
+          <t>110587; 156720</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>79771; 116282</t>
+          <t>78960; 114522</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>147226; 667445</t>
+          <t>110988; 151667</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>185300; 237694</t>
+          <t>184805; 236600</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>176324; 226799</t>
+          <t>176543; 227543</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>161588; 210249</t>
+          <t>160052; 211197</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>174763; 212498</t>
+          <t>193589; 237770</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>305647; 374031</t>
+          <t>309351; 373627</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>301293; 370896</t>
+          <t>299554; 366405</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>249191; 310155</t>
+          <t>249954; 312414</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>353009; 1003850</t>
+          <t>321662; 379043</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>932665</t>
+          <t>743776</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1025315</t>
+          <t>1127063</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1957981</t>
+          <t>1870839</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>474454; 560810</t>
+          <t>481030; 562924</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>569321; 661015</t>
+          <t>563457; 658834</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>525968; 616499</t>
+          <t>524766; 611561</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>726198; 1480569</t>
+          <t>697179; 789609</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>868738; 973390</t>
+          <t>869194; 978300</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>978146; 1093802</t>
+          <t>978744; 1093225</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>875309; 985535</t>
+          <t>867949; 987318</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>833870; 1116157</t>
+          <t>1081305; 1176427</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1362956; 1504916</t>
+          <t>1371871; 1505426</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1581308; 1725508</t>
+          <t>1581783; 1722356</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1422095; 1562434</t>
+          <t>1417794; 1563877</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1721211; 2611019</t>
+          <t>1801687; 1939504</t>
         </is>
       </c>
     </row>
